--- a/SuppXLS/Scen_Z_SYS_Additional_AssumptionsMACC.xlsx
+++ b/SuppXLS/Scen_Z_SYS_Additional_AssumptionsMACC.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F237D9C0-B5F0-4907-A37B-A0D8E80F5E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED7E09C-CE5E-493F-A5E9-41958BA24DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="29" r:id="rId1"/>
     <sheet name="Regions" sheetId="15" r:id="rId2"/>
     <sheet name="PWR" sheetId="19" r:id="rId3"/>
-    <sheet name="SYS" sheetId="28" r:id="rId4"/>
-    <sheet name="SUP" sheetId="11" r:id="rId5"/>
-    <sheet name="SRV" sheetId="26" r:id="rId6"/>
-    <sheet name="TRA" sheetId="27" r:id="rId7"/>
+    <sheet name="RSD" sheetId="30" r:id="rId4"/>
+    <sheet name="SYS" sheetId="28" r:id="rId5"/>
+    <sheet name="SUP" sheetId="11" r:id="rId6"/>
+    <sheet name="SRV" sheetId="26" r:id="rId7"/>
+    <sheet name="TRA" sheetId="27" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="__123Graph_AEUMILKPN" localSheetId="0" hidden="1">#REF!</definedName>
@@ -195,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="268">
   <si>
     <t>UC_N</t>
   </si>
@@ -1001,6 +1002,24 @@
   </si>
   <si>
     <t>TFM_INS</t>
+  </si>
+  <si>
+    <t>UC_RSD_GAS_OIL_ratio</t>
+  </si>
+  <si>
+    <t>FT-RSDKER</t>
+  </si>
+  <si>
+    <t>RSDKER</t>
+  </si>
+  <si>
+    <t>FT-RSDGAS</t>
+  </si>
+  <si>
+    <t>RSDGAS</t>
+  </si>
+  <si>
+    <t>The share ratio for natural gas and kerosene in residential sector</t>
   </si>
 </sst>
 </file>
@@ -17010,6 +17029,104 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93BCBE91-6737-4A5C-8B05-174F9388360E}">
+  <dimension ref="C4:L9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="4" spans="3:12">
+      <c r="C4" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="3:12">
+      <c r="C5" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="3:12">
+      <c r="H6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="3:12">
+      <c r="C7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="3:12" ht="30">
+      <c r="C8" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="G8" s="19">
+        <v>2025</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="I8">
+        <v>0.59</v>
+      </c>
+      <c r="J8" s="38">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>5</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="9" spans="3:12">
+      <c r="E9" t="s">
+        <v>265</v>
+      </c>
+      <c r="F9" t="s">
+        <v>266</v>
+      </c>
+      <c r="I9">
+        <f>I8-1</f>
+        <v>-0.41000000000000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DE4666E-C19A-4073-8183-3ACBB585B13C}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:J4"/>
@@ -17080,7 +17197,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:V60"/>
@@ -18155,7 +18272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F532AC2E-E047-4124-A56C-AD8CA9B97A1E}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B3:I12"/>
@@ -18373,7 +18490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8FB1178-AF9A-473D-9FB3-41C2F896D89C}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="B3:M91"/>

--- a/SuppXLS/Scen_Z_SYS_Additional_AssumptionsMACC.xlsx
+++ b/SuppXLS/Scen_Z_SYS_Additional_AssumptionsMACC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BSuleimenov\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED7E09C-CE5E-493F-A5E9-41958BA24DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2C8A27-D73E-4C66-862F-93D5B837B98E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="29" r:id="rId1"/>
@@ -11841,7 +11841,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
@@ -12300,17 +12300,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79DA532-7D5D-4233-BA89-FC4C950C7D0C}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:Z99"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" customWidth="1"/>
-    <col min="8" max="10" width="8.140625" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" customWidth="1"/>
+    <col min="1" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" customWidth="1"/>
+    <col min="8" max="10" width="8.109375" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" customWidth="1"/>
+    <col min="12" max="12" width="8.109375" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" customWidth="1"/>
+    <col min="15" max="15" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
@@ -15147,36 +15147,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F0F7499-A5CE-4374-995E-DC72D788363A}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A3:AD37"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.5703125" customWidth="1"/>
-    <col min="25" max="25" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="3.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.5546875" customWidth="1"/>
+    <col min="25" max="25" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="27" max="28" width="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:30">
@@ -15647,7 +15647,7 @@
         <v>IE-MN</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="15.75" thickBot="1">
+    <row r="10" spans="1:30" ht="15" thickBot="1">
       <c r="A10" s="13" t="s">
         <v>23</v>
       </c>
@@ -15889,7 +15889,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>3</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
@@ -15908,12 +15908,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE79BAD-EA44-47F0-A194-320DE6C9FB50}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:W62"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:23">
@@ -15999,7 +15999,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:23" ht="45">
+    <row r="6" spans="2:23" ht="43.2">
       <c r="B6" s="19" t="s">
         <v>145</v>
       </c>
@@ -16178,7 +16178,7 @@
       </c>
       <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="2:23" ht="15.75" thickBot="1">
+    <row r="16" spans="2:23" ht="15" thickBot="1">
       <c r="B16" s="8" t="s">
         <v>12</v>
       </c>
@@ -16325,7 +16325,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="15.75" thickBot="1">
+    <row r="24" spans="2:12" ht="15" thickBot="1">
       <c r="B24" s="8" t="s">
         <v>12</v>
       </c>
@@ -16595,7 +16595,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="2:12" ht="15.75" thickBot="1">
+    <row r="37" spans="2:12" ht="15" thickBot="1">
       <c r="B37" s="8" t="s">
         <v>12</v>
       </c>
@@ -17031,7 +17031,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93BCBE91-6737-4A5C-8B05-174F9388360E}">
   <dimension ref="C4:L9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="4" spans="3:12">
       <c r="C4" s="4" t="s">
@@ -17080,7 +17080,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="3:12" ht="30">
+    <row r="8" spans="3:12" ht="28.8">
       <c r="C8" s="19" t="s">
         <v>262</v>
       </c>
@@ -17130,10 +17130,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DE4666E-C19A-4073-8183-3ACBB585B13C}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:J4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
@@ -17144,7 +17144,7 @@
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" spans="2:10" ht="15.75" thickBot="1">
+    <row r="3" spans="2:10" ht="15" thickBot="1">
       <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
@@ -17201,19 +17201,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:V60"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.28515625" customWidth="1"/>
-    <col min="12" max="12" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.33203125" customWidth="1"/>
+    <col min="12" max="12" width="44.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17302,7 +17302,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="30">
+    <row r="6" spans="1:22" ht="28.8">
       <c r="B6" s="38" t="s">
         <v>111</v>
       </c>
@@ -17640,7 +17640,7 @@
     </row>
     <row r="16" spans="1:22">
       <c r="H16" t="s">
-        <v>7</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -17801,7 +17801,7 @@
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" spans="2:13" ht="15.75" thickBot="1">
+    <row r="28" spans="2:13" ht="15" thickBot="1">
       <c r="B28" s="8" t="s">
         <v>12</v>
       </c>
@@ -17890,7 +17890,7 @@
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
-    <row r="34" spans="2:13" ht="15.75" thickBot="1">
+    <row r="34" spans="2:13" ht="15" thickBot="1">
       <c r="B34" s="8" t="s">
         <v>12</v>
       </c>
@@ -18022,7 +18022,7 @@
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
     </row>
-    <row r="42" spans="2:13" ht="15.75" thickBot="1">
+    <row r="42" spans="2:13" ht="15" thickBot="1">
       <c r="B42" s="8" t="s">
         <v>12</v>
       </c>
@@ -18072,7 +18072,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15.75" thickBot="1">
+    <row r="54" spans="2:11" ht="15" thickBot="1">
       <c r="B54" s="19" t="s">
         <v>181</v>
       </c>
@@ -18276,10 +18276,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F532AC2E-E047-4124-A56C-AD8CA9B97A1E}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B3:I12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:9">
@@ -18289,7 +18289,7 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" spans="2:9" ht="15.75" thickBot="1">
+    <row r="4" spans="2:9" ht="15" thickBot="1">
       <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
@@ -18494,19 +18494,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8FB1178-AF9A-473D-9FB3-41C2F896D89C}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="B3:M91"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="22.85546875" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="6" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="28.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" customWidth="1"/>
+    <col min="5" max="6" width="11.6640625" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="28.44140625" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:13">
@@ -18516,7 +18516,7 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="2:13" ht="15.75" thickBot="1">
+    <row r="4" spans="2:13" ht="15" thickBot="1">
       <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
@@ -19527,7 +19527,7 @@
       <c r="C60" s="58"/>
       <c r="D60" s="58"/>
     </row>
-    <row r="61" spans="2:13" ht="15.75">
+    <row r="61" spans="2:13" ht="15.6">
       <c r="B61" s="58"/>
       <c r="C61" s="64">
         <v>2018</v>
@@ -19742,7 +19742,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="73" spans="2:8" ht="15.75">
+    <row r="73" spans="2:8" ht="15.6">
       <c r="B73" s="59" t="s">
         <v>214</v>
       </c>

--- a/SuppXLS/Scen_Z_SYS_Additional_AssumptionsMACC.xlsx
+++ b/SuppXLS/Scen_Z_SYS_Additional_AssumptionsMACC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BSuleimenov\Documents\GitHub\times-ireland-model\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2C8A27-D73E-4C66-862F-93D5B837B98E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFCA99D-FDEC-48D3-BEA8-0435AD9C63A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="29" r:id="rId1"/>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="266">
   <si>
     <t>UC_N</t>
   </si>
@@ -719,9 +719,6 @@
     <t>Source: CLIMATE ACTION PLAN 2023, CAP23</t>
   </si>
   <si>
-    <t>Minimum solar PV capacity</t>
-  </si>
-  <si>
     <t>Max Wind Offshore Capacity</t>
   </si>
   <si>
@@ -966,9 +963,6 @@
   </si>
   <si>
     <t>https://cms.eirgrid.ie/sites/default/files/publications/19035-EirGrid-Generation-Capacity-Statement-Combined-2023-V5-Jan-2024.pdf</t>
-  </si>
-  <si>
-    <t>FX</t>
   </si>
   <si>
     <t>UC_Min_PV_Cap</t>
@@ -11841,7 +11835,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>22860</xdr:colOff>
+          <xdr:colOff>28575</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
@@ -12300,17 +12294,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79DA532-7D5D-4233-BA89-FC4C950C7D0C}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:Z99"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" customWidth="1"/>
-    <col min="8" max="10" width="8.109375" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" customWidth="1"/>
-    <col min="12" max="12" width="8.109375" customWidth="1"/>
+    <col min="1" max="4" width="21.5703125" customWidth="1"/>
+    <col min="5" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
+    <col min="8" max="10" width="8.140625" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" customWidth="1"/>
-    <col min="15" max="15" width="13.44140625" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
@@ -15147,36 +15141,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F0F7499-A5CE-4374-995E-DC72D788363A}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A3:AD37"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.109375" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
-    <col min="3" max="3" width="3.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.5546875" customWidth="1"/>
-    <col min="25" max="25" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.5703125" customWidth="1"/>
+    <col min="25" max="25" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="28" width="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:30">
@@ -15647,7 +15639,7 @@
         <v>IE-MN</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="15" thickBot="1">
+    <row r="10" spans="1:30" ht="15.75" thickBot="1">
       <c r="A10" s="13" t="s">
         <v>23</v>
       </c>
@@ -15889,7 +15881,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>22860</xdr:colOff>
+                    <xdr:colOff>28575</xdr:colOff>
                     <xdr:row>3</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
@@ -15908,20 +15900,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE79BAD-EA44-47F0-A194-320DE6C9FB50}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:W62"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:23">
       <c r="B2" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="2:23">
@@ -15934,7 +15926,7 @@
     </row>
     <row r="4" spans="2:23">
       <c r="G4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="S4" t="s">
         <v>7</v>
@@ -15993,39 +15985,39 @@
         <v>17</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="W5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:23" ht="43.2">
+    <row r="6" spans="2:23" ht="45">
       <c r="B6" s="19" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="F6" s="19">
-        <v>2023</v>
+        <v>107</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>107</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6" s="38">
-        <v>0.8</v>
+        <v>107</v>
+      </c>
+      <c r="H6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I6" s="38" t="s">
+        <v>107</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="N6" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="P6" s="20" t="s">
         <v>193</v>
-      </c>
-      <c r="P6" s="20" t="s">
-        <v>194</v>
       </c>
       <c r="R6" s="19">
         <v>2023</v>
@@ -16043,12 +16035,12 @@
         <v>5</v>
       </c>
       <c r="W6" s="19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="2:23">
       <c r="B7" s="19" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>146</v>
@@ -16178,7 +16170,7 @@
       </c>
       <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="2:23" ht="15" thickBot="1">
+    <row r="16" spans="2:23" ht="15.75" thickBot="1">
       <c r="B16" s="8" t="s">
         <v>12</v>
       </c>
@@ -16245,12 +16237,12 @@
       </c>
       <c r="H18" s="39"/>
       <c r="I18" s="39" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J18" s="39"/>
       <c r="K18" s="39"/>
       <c r="L18" s="40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="2:12">
@@ -16273,7 +16265,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L19" s="17" t="s">
         <v>116</v>
@@ -16299,7 +16291,7 @@
         <v>5</v>
       </c>
       <c r="I20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="2:12">
@@ -16322,10 +16314,10 @@
     </row>
     <row r="23" spans="2:12">
       <c r="B23" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" ht="15" thickBot="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="15.75" thickBot="1">
       <c r="B24" s="8" t="s">
         <v>12</v>
       </c>
@@ -16374,10 +16366,10 @@
         <v>1.5</v>
       </c>
       <c r="I25" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="L25" s="40" t="s">
         <v>172</v>
-      </c>
-      <c r="L25" s="40" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -16400,10 +16392,10 @@
         <v>13.8</v>
       </c>
       <c r="I26" s="39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L26" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -16426,10 +16418,10 @@
         <v>0</v>
       </c>
       <c r="I27" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="L27" s="40" t="s">
         <v>175</v>
-      </c>
-      <c r="L27" s="40" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="28" spans="2:12">
@@ -16452,7 +16444,7 @@
         <v>5</v>
       </c>
       <c r="I28" s="39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="2:12">
@@ -16476,7 +16468,7 @@
       </c>
       <c r="H29" s="39"/>
       <c r="I29" s="39" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="2:12">
@@ -16500,7 +16492,7 @@
       </c>
       <c r="H30" s="39"/>
       <c r="I30" s="39" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="2:12">
@@ -16524,10 +16516,10 @@
       </c>
       <c r="H31" s="39"/>
       <c r="I31" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="L31" s="40" t="s">
         <v>178</v>
-      </c>
-      <c r="L31" s="40" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="32" spans="2:12">
@@ -16551,10 +16543,10 @@
       </c>
       <c r="H32" s="39"/>
       <c r="I32" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="L32" s="40" t="s">
         <v>178</v>
-      </c>
-      <c r="L32" s="40" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="33" spans="2:12">
@@ -16578,7 +16570,7 @@
       </c>
       <c r="H33" s="39"/>
       <c r="I33" s="39" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="2:12">
@@ -16595,7 +16587,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="2:12" ht="15" thickBot="1">
+    <row r="37" spans="2:12" ht="15.75" thickBot="1">
       <c r="B37" s="8" t="s">
         <v>12</v>
       </c>
@@ -16809,7 +16801,7 @@
         <v>0.2</v>
       </c>
       <c r="J50" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="2:10">
@@ -16832,7 +16824,7 @@
         <v>1.5</v>
       </c>
       <c r="J51" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="2:10">
@@ -16855,7 +16847,7 @@
         <v>3</v>
       </c>
       <c r="J52" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53" spans="2:10">
@@ -16878,7 +16870,7 @@
         <v>6</v>
       </c>
       <c r="J53" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="2:10">
@@ -16901,7 +16893,7 @@
         <v>8</v>
       </c>
       <c r="J54" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="2:10">
@@ -16926,7 +16918,7 @@
         <v>10</v>
       </c>
       <c r="J55" s="44" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="2:10">
@@ -17014,7 +17006,7 @@
         <v>166</v>
       </c>
       <c r="J62" s="85" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -17031,11 +17023,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93BCBE91-6737-4A5C-8B05-174F9388360E}">
   <dimension ref="C4:L9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="4" spans="3:12">
       <c r="C4" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="3:12">
@@ -17071,24 +17063,24 @@
         <v>112</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="3:12" ht="28.8">
+    <row r="8" spans="3:12" ht="30">
       <c r="C8" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="F8" s="19" t="s">
         <v>262</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>264</v>
       </c>
       <c r="G8" s="19">
         <v>2025</v>
@@ -17097,7 +17089,7 @@
         <v>164</v>
       </c>
       <c r="I8">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
       <c r="J8" s="38">
         <v>0</v>
@@ -17106,19 +17098,19 @@
         <v>5</v>
       </c>
       <c r="L8" s="19" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="3:12">
       <c r="E9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F9" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I9">
         <f>I8-1</f>
-        <v>-0.41000000000000003</v>
+        <v>-0.59000000000000008</v>
       </c>
     </row>
   </sheetData>
@@ -17130,10 +17122,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DE4666E-C19A-4073-8183-3ACBB585B13C}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:J4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
@@ -17144,7 +17136,7 @@
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" spans="2:10" ht="15" thickBot="1">
+    <row r="3" spans="2:10" ht="15.75" thickBot="1">
       <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
@@ -17201,19 +17193,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:V60"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.33203125" customWidth="1"/>
-    <col min="12" max="12" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.42578125" customWidth="1"/>
+    <col min="12" max="12" width="44.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17302,13 +17294,13 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="28.8">
+    <row r="6" spans="1:22" ht="30">
       <c r="B6" s="38" t="s">
         <v>111</v>
       </c>
       <c r="C6" s="39"/>
       <c r="D6" s="42" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E6" s="39"/>
       <c r="F6" s="39"/>
@@ -17325,7 +17317,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="38" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M6" s="19" t="s">
         <v>111</v>
@@ -17640,7 +17632,7 @@
     </row>
     <row r="16" spans="1:22">
       <c r="H16" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -17801,7 +17793,7 @@
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" spans="2:13" ht="15" thickBot="1">
+    <row r="28" spans="2:13" ht="15.75" thickBot="1">
       <c r="B28" s="8" t="s">
         <v>12</v>
       </c>
@@ -17890,7 +17882,7 @@
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
-    <row r="34" spans="2:13" ht="15" thickBot="1">
+    <row r="34" spans="2:13" ht="15.75" thickBot="1">
       <c r="B34" s="8" t="s">
         <v>12</v>
       </c>
@@ -18022,7 +18014,7 @@
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
     </row>
-    <row r="42" spans="2:13" ht="15" thickBot="1">
+    <row r="42" spans="2:13" ht="15.75" thickBot="1">
       <c r="B42" s="8" t="s">
         <v>12</v>
       </c>
@@ -18069,18 +18061,18 @@
     </row>
     <row r="53" spans="2:11">
       <c r="E53" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B54" s="19" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="54" spans="2:11" ht="15" thickBot="1">
-      <c r="B54" s="19" t="s">
+      <c r="C54" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="C54" s="52" t="s">
+      <c r="D54" s="52" t="s">
         <v>182</v>
-      </c>
-      <c r="D54" s="52" t="s">
-        <v>183</v>
       </c>
       <c r="E54" s="52">
         <v>2020</v>
@@ -18106,7 +18098,7 @@
     </row>
     <row r="55" spans="2:11">
       <c r="B55" s="45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C55" s="19">
         <v>34.700000000000003</v>
@@ -18138,7 +18130,7 @@
     </row>
     <row r="56" spans="2:11">
       <c r="B56" s="43" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C56" s="19">
         <v>34.700000000000003</v>
@@ -18170,7 +18162,7 @@
     </row>
     <row r="57" spans="2:11">
       <c r="B57" s="43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C57" s="19">
         <v>36.6</v>
@@ -18202,7 +18194,7 @@
     </row>
     <row r="58" spans="2:11">
       <c r="B58" s="46" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C58" s="44">
         <v>40.299999999999997</v>
@@ -18235,7 +18227,7 @@
     <row r="59" spans="2:11">
       <c r="C59" s="47"/>
       <c r="D59" s="47" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E59" s="47">
         <v>1.8</v>
@@ -18261,10 +18253,10 @@
     </row>
     <row r="60" spans="2:11">
       <c r="B60" s="50" t="s">
+        <v>188</v>
+      </c>
+      <c r="C60" s="51" t="s">
         <v>189</v>
-      </c>
-      <c r="C60" s="51" t="s">
-        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -18276,10 +18268,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F532AC2E-E047-4124-A56C-AD8CA9B97A1E}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B3:I12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:9">
@@ -18289,7 +18281,7 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" spans="2:9" ht="15" thickBot="1">
+    <row r="4" spans="2:9" ht="15.75" thickBot="1">
       <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
@@ -18494,29 +18486,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8FB1178-AF9A-473D-9FB3-41C2F896D89C}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="B3:M91"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="22.88671875" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" customWidth="1"/>
-    <col min="5" max="6" width="11.6640625" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" customWidth="1"/>
-    <col min="11" max="11" width="28.44140625" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="6" width="11.5703125" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" customWidth="1"/>
+    <col min="11" max="11" width="28.42578125" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:13">
       <c r="B3" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="2:13" ht="15" thickBot="1">
+    <row r="4" spans="2:13" ht="15.75" thickBot="1">
       <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
@@ -18555,7 +18547,7 @@
         <v>104</v>
       </c>
       <c r="H5" s="86" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I5" s="86" t="str">
         <f>H5</f>
@@ -18596,13 +18588,13 @@
         <v>0</v>
       </c>
       <c r="C14" s="77" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D14" s="77" t="s">
         <v>3</v>
       </c>
       <c r="E14" s="77" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F14" s="77" t="s">
         <v>2</v>
@@ -18611,39 +18603,39 @@
         <v>9</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I14" s="78" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J14" s="78" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K14" s="76" t="s">
         <v>11</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C15" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F15" s="19">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G15" s="19" t="s">
         <v>164</v>
@@ -18659,7 +18651,7 @@
         <v>5</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -18671,10 +18663,10 @@
     <row r="16" spans="2:13">
       <c r="B16" s="19"/>
       <c r="D16" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F16" s="19">
         <v>2030</v>
@@ -18695,10 +18687,10 @@
     <row r="17" spans="2:13">
       <c r="B17" s="19"/>
       <c r="D17" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F17" s="19">
         <v>2051</v>
@@ -18717,19 +18709,19 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C18" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F18" s="19">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G18" s="19" t="s">
         <v>81</v>
@@ -18745,7 +18737,7 @@
         <v>5</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -18757,10 +18749,10 @@
     <row r="19" spans="2:13">
       <c r="B19" s="19"/>
       <c r="D19" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F19" s="19">
         <v>2030</v>
@@ -18782,10 +18774,10 @@
       <c r="B20" s="44"/>
       <c r="C20" s="18"/>
       <c r="D20" s="81" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F20" s="44">
         <v>2050</v>
@@ -18837,13 +18829,13 @@
         <v>0</v>
       </c>
       <c r="C26" s="77" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D26" s="77" t="s">
         <v>3</v>
       </c>
       <c r="E26" s="77" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F26" s="77" t="s">
         <v>2</v>
@@ -18852,39 +18844,39 @@
         <v>9</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I26" s="78" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J26" s="78" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K26" s="76" t="s">
         <v>11</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="19" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C27" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E27" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F27" s="19">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G27" s="19" t="s">
         <v>164</v>
@@ -18900,7 +18892,7 @@
         <v>5</v>
       </c>
       <c r="K27" s="19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -18912,10 +18904,10 @@
     <row r="28" spans="2:13">
       <c r="B28" s="19"/>
       <c r="D28" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F28" s="19">
         <v>2040</v>
@@ -18934,10 +18926,10 @@
     <row r="29" spans="2:13">
       <c r="B29" s="19"/>
       <c r="D29" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F29" s="19">
         <v>2055</v>
@@ -18955,19 +18947,19 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C30" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E30" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F30" s="19">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G30" s="19" t="s">
         <v>81</v>
@@ -18983,7 +18975,7 @@
         <v>5</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -18996,10 +18988,10 @@
       <c r="B31" s="44"/>
       <c r="C31" s="18"/>
       <c r="D31" s="81" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F31" s="44">
         <v>2040</v>
@@ -19019,10 +19011,10 @@
     </row>
     <row r="32" spans="2:13">
       <c r="D32" s="81" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F32" s="44">
         <v>2050</v>
@@ -19069,13 +19061,13 @@
         <v>0</v>
       </c>
       <c r="C38" s="77" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D38" s="77" t="s">
         <v>3</v>
       </c>
       <c r="E38" s="77" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F38" s="77" t="s">
         <v>2</v>
@@ -19084,39 +19076,39 @@
         <v>9</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I38" s="78" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J38" s="78" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K38" s="76" t="s">
         <v>11</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C39" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E39" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F39" s="19">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G39" s="19" t="s">
         <v>164</v>
@@ -19132,7 +19124,7 @@
         <v>5</v>
       </c>
       <c r="K39" s="19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -19144,10 +19136,10 @@
     <row r="40" spans="2:13">
       <c r="B40" s="19"/>
       <c r="D40" s="20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E40" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F40" s="19">
         <v>2040</v>
@@ -19167,10 +19159,10 @@
     <row r="41" spans="2:13">
       <c r="B41" s="19"/>
       <c r="D41" s="20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E41" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F41" s="19">
         <v>2055</v>
@@ -19189,19 +19181,19 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="19" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C42" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E42" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F42" s="19">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G42" s="19" t="s">
         <v>81</v>
@@ -19217,7 +19209,7 @@
         <v>5</v>
       </c>
       <c r="K42" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -19230,10 +19222,10 @@
       <c r="B43" s="44"/>
       <c r="C43" s="18"/>
       <c r="D43" s="81" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F43" s="44">
         <v>2040</v>
@@ -19253,10 +19245,10 @@
     </row>
     <row r="44" spans="2:13">
       <c r="D44" s="81" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F44" s="44">
         <v>2050</v>
@@ -19308,13 +19300,13 @@
         <v>0</v>
       </c>
       <c r="C50" s="77" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D50" s="77" t="s">
         <v>3</v>
       </c>
       <c r="E50" s="77" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F50" s="77" t="s">
         <v>2</v>
@@ -19323,39 +19315,39 @@
         <v>9</v>
       </c>
       <c r="H50" s="18" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I50" s="78" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J50" s="78" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K50" s="76" t="s">
         <v>11</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C51" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F51" s="19">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G51" s="19" t="s">
         <v>164</v>
@@ -19371,7 +19363,7 @@
         <v>5</v>
       </c>
       <c r="K51" s="19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -19383,10 +19375,10 @@
     <row r="52" spans="2:13">
       <c r="B52" s="19"/>
       <c r="D52" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E52" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F52" s="19">
         <v>2040</v>
@@ -19402,16 +19394,16 @@
       </c>
       <c r="J52" s="19"/>
       <c r="K52" s="19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="53" spans="2:13">
       <c r="B53" s="19"/>
       <c r="D53" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E53" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F53" s="19">
         <v>2051</v>
@@ -19430,19 +19422,19 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C54" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D54" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E54" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F54" s="19">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G54" s="19" t="s">
         <v>81</v>
@@ -19458,7 +19450,7 @@
         <v>5</v>
       </c>
       <c r="K54" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -19471,10 +19463,10 @@
       <c r="B55" s="44"/>
       <c r="C55" s="18"/>
       <c r="D55" s="81" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F55" s="44">
         <v>2040</v>
@@ -19491,15 +19483,15 @@
       </c>
       <c r="J55" s="44"/>
       <c r="K55" s="44" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="56" spans="2:13">
       <c r="D56" s="81" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F56" s="44">
         <v>2050</v>
@@ -19522,12 +19514,12 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="58" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C60" s="58"/>
       <c r="D60" s="58"/>
     </row>
-    <row r="61" spans="2:13" ht="15.6">
+    <row r="61" spans="2:13" ht="15.75">
       <c r="B61" s="58"/>
       <c r="C61" s="64">
         <v>2018</v>
@@ -19550,7 +19542,7 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="59" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C62" s="60">
         <v>121157</v>
@@ -19573,7 +19565,7 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="59" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C63" s="60">
         <v>25459</v>
@@ -19596,7 +19588,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="59" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C64" s="60">
         <v>157865</v>
@@ -19619,7 +19611,7 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" s="59" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C65" s="63">
         <v>304481</v>
@@ -19642,7 +19634,7 @@
     </row>
     <row r="66" spans="2:8">
       <c r="B66" s="59" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C66" s="60">
         <v>99456</v>
@@ -19665,7 +19657,7 @@
     </row>
     <row r="67" spans="2:8">
       <c r="B67" s="59" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C67" s="60">
         <v>14859</v>
@@ -19688,7 +19680,7 @@
     </row>
     <row r="68" spans="2:8">
       <c r="B68" s="59" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C68" s="60">
         <v>125874</v>
@@ -19711,7 +19703,7 @@
     </row>
     <row r="69" spans="2:8">
       <c r="B69" s="61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C69" s="62">
         <v>240189</v>
@@ -19734,17 +19726,17 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" s="59" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" s="65" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" ht="15.75">
+      <c r="B73" s="59" t="s">
         <v>213</v>
-      </c>
-    </row>
-    <row r="73" spans="2:8" ht="15.6">
-      <c r="B73" s="59" t="s">
-        <v>214</v>
       </c>
       <c r="C73" s="64">
         <v>2018</v>
@@ -19767,7 +19759,7 @@
     </row>
     <row r="74" spans="2:8">
       <c r="B74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C74" s="56">
         <f>C62+C66</f>
@@ -19796,7 +19788,7 @@
     </row>
     <row r="75" spans="2:8">
       <c r="B75" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C75" s="56">
         <f>C63+C67</f>
@@ -19825,7 +19817,7 @@
     </row>
     <row r="76" spans="2:8">
       <c r="B76" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C76" s="56">
         <f>C75*$G$88</f>
@@ -19854,7 +19846,7 @@
     </row>
     <row r="77" spans="2:8">
       <c r="B77" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C77" s="56">
         <f>C75*$G$89</f>
@@ -19883,7 +19875,7 @@
     </row>
     <row r="78" spans="2:8">
       <c r="B78" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C78" s="56">
         <f>C75*$G$90</f>
@@ -19912,15 +19904,15 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="83" spans="2:8">
       <c r="B83" s="67" t="s">
+        <v>220</v>
+      </c>
+      <c r="C83" s="68" t="s">
         <v>221</v>
-      </c>
-      <c r="C83" s="68" t="s">
-        <v>222</v>
       </c>
       <c r="G83">
         <v>2022</v>
@@ -19931,13 +19923,13 @@
     </row>
     <row r="84" spans="2:8">
       <c r="B84" s="69" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C84" s="70">
         <v>387723</v>
       </c>
       <c r="F84" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G84">
         <f>C85+C86</f>
@@ -19949,13 +19941,13 @@
     </row>
     <row r="85" spans="2:8">
       <c r="B85" s="71" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C85" s="72">
         <v>222953</v>
       </c>
       <c r="F85" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G85">
         <f>C87+C88</f>
@@ -19967,13 +19959,13 @@
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="69" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C86" s="70">
         <v>127727</v>
       </c>
       <c r="F86" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G86">
         <f>C89+C90</f>
@@ -19985,24 +19977,24 @@
     </row>
     <row r="87" spans="2:8">
       <c r="B87" s="71" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C87" s="72">
         <v>4421</v>
       </c>
       <c r="G87" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="88" spans="2:8">
       <c r="B88" s="69" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C88" s="70">
         <v>6802</v>
       </c>
       <c r="F88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G88" s="54">
         <f>G84/$C$84</f>
@@ -20011,13 +20003,13 @@
     </row>
     <row r="89" spans="2:8">
       <c r="B89" s="71" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C89" s="72">
         <v>9100</v>
       </c>
       <c r="F89" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G89" s="54">
         <f t="shared" ref="G89:G90" si="5">G85/$C$84</f>
@@ -20026,13 +20018,13 @@
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C90" s="66">
         <v>16721</v>
       </c>
       <c r="F90" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G90" s="54">
         <f t="shared" si="5"/>
@@ -20041,7 +20033,7 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="57" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
